--- a/dev/epa_monitoring_data_K_2025-05-27_to_2026-05-26.xlsx
+++ b/dev/epa_monitoring_data_K_2025-05-27_to_2026-05-26.xlsx
@@ -386,7 +386,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:H378"/>
+  <dimension ref="A1:H407"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
@@ -455,6 +455,9 @@
           <t>per cent by volume</t>
         </is>
       </c>
+      <c r="D2">
+        <v>4</v>
+      </c>
       <c r="E2">
         <v>178</v>
       </c>
@@ -1499,6 +1502,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D38">
+        <v>4</v>
+      </c>
       <c r="E38">
         <v>3</v>
       </c>
@@ -1760,6 +1766,9 @@
           <t>microsiemens per centimetre</t>
         </is>
       </c>
+      <c r="D47">
+        <v>4</v>
+      </c>
       <c r="E47">
         <v>3</v>
       </c>
@@ -2050,6 +2059,9 @@
           <t>pH units</t>
         </is>
       </c>
+      <c r="D57">
+        <v>4</v>
+      </c>
       <c r="E57">
         <v>3</v>
       </c>
@@ -2079,6 +2091,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D58">
+        <v>4</v>
+      </c>
       <c r="E58">
         <v>3</v>
       </c>
@@ -2166,6 +2181,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D61">
+        <v>4</v>
+      </c>
       <c r="E61">
         <v>3</v>
       </c>
@@ -2195,6 +2213,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D62">
+        <v>4</v>
+      </c>
       <c r="E62">
         <v>3</v>
       </c>
@@ -2311,6 +2332,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D66">
+        <v>4</v>
+      </c>
       <c r="E66">
         <v>11</v>
       </c>
@@ -2572,6 +2596,9 @@
           <t>microsiemens per centimetre</t>
         </is>
       </c>
+      <c r="D75">
+        <v>4</v>
+      </c>
       <c r="E75">
         <v>3</v>
       </c>
@@ -2862,6 +2889,9 @@
           <t>pH units</t>
         </is>
       </c>
+      <c r="D85">
+        <v>4</v>
+      </c>
       <c r="E85">
         <v>5</v>
       </c>
@@ -2891,6 +2921,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D86">
+        <v>4</v>
+      </c>
       <c r="E86">
         <v>3</v>
       </c>
@@ -2978,6 +3011,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D89">
+        <v>4</v>
+      </c>
       <c r="E89">
         <v>3</v>
       </c>
@@ -3007,6 +3043,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D90">
+        <v>4</v>
+      </c>
       <c r="E90">
         <v>3</v>
       </c>
@@ -3123,6 +3162,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D94">
+        <v>4</v>
+      </c>
       <c r="E94">
         <v>9</v>
       </c>
@@ -3384,6 +3426,9 @@
           <t>microsiemens per centimetre</t>
         </is>
       </c>
+      <c r="D103">
+        <v>4</v>
+      </c>
       <c r="E103">
         <v>3</v>
       </c>
@@ -3674,6 +3719,9 @@
           <t>pH units</t>
         </is>
       </c>
+      <c r="D113">
+        <v>4</v>
+      </c>
       <c r="E113">
         <v>5</v>
       </c>
@@ -3732,6 +3780,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D115">
+        <v>4</v>
+      </c>
       <c r="E115">
         <v>3</v>
       </c>
@@ -3819,6 +3870,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D118">
+        <v>4</v>
+      </c>
       <c r="E118">
         <v>3</v>
       </c>
@@ -3848,6 +3902,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D119">
+        <v>4</v>
+      </c>
       <c r="E119">
         <v>3</v>
       </c>
@@ -3964,6 +4021,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D123">
+        <v>4</v>
+      </c>
       <c r="E123">
         <v>3</v>
       </c>
@@ -4196,6 +4256,9 @@
           <t>microsiemens per centimetre</t>
         </is>
       </c>
+      <c r="D131">
+        <v>4</v>
+      </c>
       <c r="E131">
         <v>1</v>
       </c>
@@ -4486,6 +4549,9 @@
           <t>pH units</t>
         </is>
       </c>
+      <c r="D141">
+        <v>4</v>
+      </c>
       <c r="E141">
         <v>2</v>
       </c>
@@ -4544,6 +4610,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D143">
+        <v>4</v>
+      </c>
       <c r="E143">
         <v>1</v>
       </c>
@@ -4631,6 +4700,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D146">
+        <v>4</v>
+      </c>
       <c r="E146">
         <v>1</v>
       </c>
@@ -4747,6 +4819,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D150">
+        <v>4</v>
+      </c>
       <c r="E150">
         <v>11</v>
       </c>
@@ -4834,6 +4909,9 @@
           <t>microsiemens per centimetre</t>
         </is>
       </c>
+      <c r="D153">
+        <v>4</v>
+      </c>
       <c r="E153">
         <v>11</v>
       </c>
@@ -4979,6 +5057,9 @@
           <t>pH units</t>
         </is>
       </c>
+      <c r="D158">
+        <v>4</v>
+      </c>
       <c r="E158">
         <v>12</v>
       </c>
@@ -5037,6 +5118,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D160">
+        <v>4</v>
+      </c>
       <c r="E160">
         <v>11</v>
       </c>
@@ -5124,6 +5208,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D163">
+        <v>4</v>
+      </c>
       <c r="E163">
         <v>11</v>
       </c>
@@ -5153,6 +5240,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D164">
+        <v>4</v>
+      </c>
       <c r="E164">
         <v>1</v>
       </c>
@@ -5385,6 +5475,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D172">
+        <v>4</v>
+      </c>
       <c r="E172">
         <v>11</v>
       </c>
@@ -5704,6 +5797,9 @@
           <t>microsiemens per centimetre</t>
         </is>
       </c>
+      <c r="D183">
+        <v>4</v>
+      </c>
       <c r="E183">
         <v>11</v>
       </c>
@@ -6516,6 +6612,9 @@
           <t>pH units</t>
         </is>
       </c>
+      <c r="D211">
+        <v>4</v>
+      </c>
       <c r="E211">
         <v>11</v>
       </c>
@@ -6603,6 +6702,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D214">
+        <v>4</v>
+      </c>
       <c r="E214">
         <v>11</v>
       </c>
@@ -6719,6 +6821,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D218">
+        <v>4</v>
+      </c>
       <c r="E218">
         <v>11</v>
       </c>
@@ -6748,6 +6853,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D219">
+        <v>4</v>
+      </c>
       <c r="E219">
         <v>1</v>
       </c>
@@ -7212,6 +7320,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D235">
+        <v>4</v>
+      </c>
       <c r="E235">
         <v>3</v>
       </c>
@@ -7241,6 +7352,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D236">
+        <v>4</v>
+      </c>
       <c r="E236">
         <v>3</v>
       </c>
@@ -7270,6 +7384,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D237">
+        <v>1</v>
+      </c>
       <c r="E237">
         <v>3</v>
       </c>
@@ -7299,6 +7416,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D238">
+        <v>1</v>
+      </c>
       <c r="E238">
         <v>3</v>
       </c>
@@ -7328,6 +7448,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D239">
+        <v>1</v>
+      </c>
       <c r="E239">
         <v>3</v>
       </c>
@@ -7357,6 +7480,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D240">
+        <v>4</v>
+      </c>
       <c r="E240">
         <v>3</v>
       </c>
@@ -7386,6 +7512,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D241">
+        <v>4</v>
+      </c>
       <c r="E241">
         <v>3</v>
       </c>
@@ -7415,6 +7544,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D242">
+        <v>1</v>
+      </c>
       <c r="E242">
         <v>3</v>
       </c>
@@ -7444,6 +7576,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D243">
+        <v>1</v>
+      </c>
       <c r="E243">
         <v>3</v>
       </c>
@@ -7473,6 +7608,9 @@
           <t>microsiemens per centimetre</t>
         </is>
       </c>
+      <c r="D244">
+        <v>4</v>
+      </c>
       <c r="E244">
         <v>3</v>
       </c>
@@ -7502,6 +7640,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D245">
+        <v>1</v>
+      </c>
       <c r="E245">
         <v>3</v>
       </c>
@@ -7531,6 +7672,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D246">
+        <v>4</v>
+      </c>
       <c r="E246">
         <v>3</v>
       </c>
@@ -7560,6 +7704,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D247">
+        <v>1</v>
+      </c>
       <c r="E247">
         <v>3</v>
       </c>
@@ -7589,6 +7736,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D248">
+        <v>4</v>
+      </c>
       <c r="E248">
         <v>3</v>
       </c>
@@ -7618,6 +7768,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D249">
+        <v>1</v>
+      </c>
       <c r="E249">
         <v>3</v>
       </c>
@@ -7647,6 +7800,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D250">
+        <v>1</v>
+      </c>
       <c r="E250">
         <v>3</v>
       </c>
@@ -7676,6 +7832,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D251">
+        <v>1</v>
+      </c>
       <c r="E251">
         <v>3</v>
       </c>
@@ -7705,6 +7864,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D252">
+        <v>4</v>
+      </c>
       <c r="E252">
         <v>3</v>
       </c>
@@ -7734,6 +7896,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D253">
+        <v>4</v>
+      </c>
       <c r="E253">
         <v>3</v>
       </c>
@@ -7763,6 +7928,9 @@
           <t>pH units</t>
         </is>
       </c>
+      <c r="D254">
+        <v>4</v>
+      </c>
       <c r="E254">
         <v>3</v>
       </c>
@@ -7792,6 +7960,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D255">
+        <v>4</v>
+      </c>
       <c r="E255">
         <v>3</v>
       </c>
@@ -7821,6 +7992,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D256">
+        <v>4</v>
+      </c>
       <c r="E256">
         <v>3</v>
       </c>
@@ -7850,6 +8024,9 @@
           <t>metres</t>
         </is>
       </c>
+      <c r="D257">
+        <v>4</v>
+      </c>
       <c r="E257">
         <v>1</v>
       </c>
@@ -7879,6 +8056,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D258">
+        <v>4</v>
+      </c>
       <c r="E258">
         <v>3</v>
       </c>
@@ -7908,6 +8088,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D259">
+        <v>4</v>
+      </c>
       <c r="E259">
         <v>3</v>
       </c>
@@ -7937,6 +8120,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D260">
+        <v>4</v>
+      </c>
       <c r="E260">
         <v>1</v>
       </c>
@@ -7966,6 +8152,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D261">
+        <v>1</v>
+      </c>
       <c r="E261">
         <v>3</v>
       </c>
@@ -7995,6 +8184,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D262">
+        <v>4</v>
+      </c>
       <c r="E262">
         <v>2</v>
       </c>
@@ -8024,6 +8216,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D263">
+        <v>4</v>
+      </c>
       <c r="E263">
         <v>2</v>
       </c>
@@ -8053,6 +8248,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D264">
+        <v>1</v>
+      </c>
       <c r="E264">
         <v>2</v>
       </c>
@@ -8082,6 +8280,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D265">
+        <v>1</v>
+      </c>
       <c r="E265">
         <v>2</v>
       </c>
@@ -8111,6 +8312,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D266">
+        <v>1</v>
+      </c>
       <c r="E266">
         <v>2</v>
       </c>
@@ -8140,6 +8344,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D267">
+        <v>4</v>
+      </c>
       <c r="E267">
         <v>2</v>
       </c>
@@ -8169,6 +8376,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D268">
+        <v>4</v>
+      </c>
       <c r="E268">
         <v>2</v>
       </c>
@@ -8198,6 +8408,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D269">
+        <v>1</v>
+      </c>
       <c r="E269">
         <v>2</v>
       </c>
@@ -8227,6 +8440,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D270">
+        <v>1</v>
+      </c>
       <c r="E270">
         <v>2</v>
       </c>
@@ -8256,6 +8472,9 @@
           <t>microsiemens per centimetre</t>
         </is>
       </c>
+      <c r="D271">
+        <v>4</v>
+      </c>
       <c r="E271">
         <v>2</v>
       </c>
@@ -8285,6 +8504,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D272">
+        <v>1</v>
+      </c>
       <c r="E272">
         <v>2</v>
       </c>
@@ -8314,6 +8536,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D273">
+        <v>4</v>
+      </c>
       <c r="E273">
         <v>2</v>
       </c>
@@ -8343,6 +8568,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D274">
+        <v>1</v>
+      </c>
       <c r="E274">
         <v>2</v>
       </c>
@@ -8372,6 +8600,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D275">
+        <v>4</v>
+      </c>
       <c r="E275">
         <v>2</v>
       </c>
@@ -8401,6 +8632,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D276">
+        <v>1</v>
+      </c>
       <c r="E276">
         <v>2</v>
       </c>
@@ -8430,6 +8664,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D277">
+        <v>1</v>
+      </c>
       <c r="E277">
         <v>2</v>
       </c>
@@ -8459,6 +8696,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D278">
+        <v>1</v>
+      </c>
       <c r="E278">
         <v>2</v>
       </c>
@@ -8488,6 +8728,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D279">
+        <v>4</v>
+      </c>
       <c r="E279">
         <v>2</v>
       </c>
@@ -8517,6 +8760,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D280">
+        <v>4</v>
+      </c>
       <c r="E280">
         <v>2</v>
       </c>
@@ -8546,6 +8792,9 @@
           <t>pH units</t>
         </is>
       </c>
+      <c r="D281">
+        <v>4</v>
+      </c>
       <c r="E281">
         <v>3</v>
       </c>
@@ -8575,6 +8824,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D282">
+        <v>4</v>
+      </c>
       <c r="E282">
         <v>2</v>
       </c>
@@ -8604,6 +8856,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D283">
+        <v>4</v>
+      </c>
       <c r="E283">
         <v>2</v>
       </c>
@@ -8633,6 +8888,9 @@
           <t>metres</t>
         </is>
       </c>
+      <c r="D284">
+        <v>4</v>
+      </c>
       <c r="E284">
         <v>1</v>
       </c>
@@ -8662,6 +8920,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D285">
+        <v>4</v>
+      </c>
       <c r="E285">
         <v>2</v>
       </c>
@@ -8691,6 +8952,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D286">
+        <v>4</v>
+      </c>
       <c r="E286">
         <v>2</v>
       </c>
@@ -8720,6 +8984,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D287">
+        <v>4</v>
+      </c>
       <c r="E287">
         <v>1</v>
       </c>
@@ -8749,6 +9016,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D288">
+        <v>1</v>
+      </c>
       <c r="E288">
         <v>2</v>
       </c>
@@ -8778,6 +9048,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D289">
+        <v>4</v>
+      </c>
       <c r="E289">
         <v>3</v>
       </c>
@@ -8807,6 +9080,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D290">
+        <v>4</v>
+      </c>
       <c r="E290">
         <v>3</v>
       </c>
@@ -8836,6 +9112,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D291">
+        <v>1</v>
+      </c>
       <c r="E291">
         <v>3</v>
       </c>
@@ -8865,6 +9144,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D292">
+        <v>1</v>
+      </c>
       <c r="E292">
         <v>3</v>
       </c>
@@ -8923,6 +9205,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D294">
+        <v>1</v>
+      </c>
       <c r="E294">
         <v>3</v>
       </c>
@@ -8952,6 +9237,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D295">
+        <v>4</v>
+      </c>
       <c r="E295">
         <v>3</v>
       </c>
@@ -8981,6 +9269,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D296">
+        <v>4</v>
+      </c>
       <c r="E296">
         <v>3</v>
       </c>
@@ -9010,6 +9301,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D297">
+        <v>1</v>
+      </c>
       <c r="E297">
         <v>3</v>
       </c>
@@ -9039,6 +9333,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D298">
+        <v>1</v>
+      </c>
       <c r="E298">
         <v>3</v>
       </c>
@@ -9068,6 +9365,9 @@
           <t>microsiemens per centimetre</t>
         </is>
       </c>
+      <c r="D299">
+        <v>4</v>
+      </c>
       <c r="E299">
         <v>3</v>
       </c>
@@ -9097,6 +9397,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D300">
+        <v>1</v>
+      </c>
       <c r="E300">
         <v>3</v>
       </c>
@@ -9126,6 +9429,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D301">
+        <v>4</v>
+      </c>
       <c r="E301">
         <v>3</v>
       </c>
@@ -9155,6 +9461,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D302">
+        <v>1</v>
+      </c>
       <c r="E302">
         <v>3</v>
       </c>
@@ -9184,6 +9493,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D303">
+        <v>4</v>
+      </c>
       <c r="E303">
         <v>3</v>
       </c>
@@ -9213,6 +9525,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D304">
+        <v>1</v>
+      </c>
       <c r="E304">
         <v>3</v>
       </c>
@@ -9242,6 +9557,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D305">
+        <v>1</v>
+      </c>
       <c r="E305">
         <v>3</v>
       </c>
@@ -9271,6 +9589,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D306">
+        <v>1</v>
+      </c>
       <c r="E306">
         <v>3</v>
       </c>
@@ -9300,6 +9621,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D307">
+        <v>4</v>
+      </c>
       <c r="E307">
         <v>3</v>
       </c>
@@ -9329,6 +9653,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D308">
+        <v>4</v>
+      </c>
       <c r="E308">
         <v>3</v>
       </c>
@@ -9358,6 +9685,9 @@
           <t>pH units</t>
         </is>
       </c>
+      <c r="D309">
+        <v>4</v>
+      </c>
       <c r="E309">
         <v>3</v>
       </c>
@@ -9387,6 +9717,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D310">
+        <v>4</v>
+      </c>
       <c r="E310">
         <v>3</v>
       </c>
@@ -9416,6 +9749,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D311">
+        <v>4</v>
+      </c>
       <c r="E311">
         <v>3</v>
       </c>
@@ -9445,6 +9781,9 @@
           <t>metres</t>
         </is>
       </c>
+      <c r="D312">
+        <v>4</v>
+      </c>
       <c r="E312">
         <v>1</v>
       </c>
@@ -9474,6 +9813,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D313">
+        <v>4</v>
+      </c>
       <c r="E313">
         <v>3</v>
       </c>
@@ -9503,6 +9845,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D314">
+        <v>4</v>
+      </c>
       <c r="E314">
         <v>3</v>
       </c>
@@ -9532,6 +9877,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D315">
+        <v>4</v>
+      </c>
       <c r="E315">
         <v>3</v>
       </c>
@@ -9590,6 +9938,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D317">
+        <v>1</v>
+      </c>
       <c r="E317">
         <v>3</v>
       </c>
@@ -9619,6 +9970,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D318">
+        <v>4</v>
+      </c>
       <c r="E318">
         <v>3</v>
       </c>
@@ -9648,6 +10002,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D319">
+        <v>4</v>
+      </c>
       <c r="E319">
         <v>3</v>
       </c>
@@ -9677,6 +10034,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D320">
+        <v>1</v>
+      </c>
       <c r="E320">
         <v>3</v>
       </c>
@@ -9706,6 +10066,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D321">
+        <v>1</v>
+      </c>
       <c r="E321">
         <v>3</v>
       </c>
@@ -9764,6 +10127,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D323">
+        <v>1</v>
+      </c>
       <c r="E323">
         <v>3</v>
       </c>
@@ -9793,6 +10159,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D324">
+        <v>4</v>
+      </c>
       <c r="E324">
         <v>3</v>
       </c>
@@ -9822,6 +10191,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D325">
+        <v>4</v>
+      </c>
       <c r="E325">
         <v>3</v>
       </c>
@@ -9851,6 +10223,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D326">
+        <v>1</v>
+      </c>
       <c r="E326">
         <v>3</v>
       </c>
@@ -9880,6 +10255,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D327">
+        <v>1</v>
+      </c>
       <c r="E327">
         <v>3</v>
       </c>
@@ -9909,6 +10287,9 @@
           <t>microsiemens per centimetre</t>
         </is>
       </c>
+      <c r="D328">
+        <v>4</v>
+      </c>
       <c r="E328">
         <v>3</v>
       </c>
@@ -9938,6 +10319,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D329">
+        <v>1</v>
+      </c>
       <c r="E329">
         <v>3</v>
       </c>
@@ -9967,6 +10351,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D330">
+        <v>4</v>
+      </c>
       <c r="E330">
         <v>3</v>
       </c>
@@ -9996,6 +10383,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D331">
+        <v>1</v>
+      </c>
       <c r="E331">
         <v>3</v>
       </c>
@@ -10025,6 +10415,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D332">
+        <v>4</v>
+      </c>
       <c r="E332">
         <v>3</v>
       </c>
@@ -10054,6 +10447,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D333">
+        <v>1</v>
+      </c>
       <c r="E333">
         <v>3</v>
       </c>
@@ -10083,6 +10479,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D334">
+        <v>1</v>
+      </c>
       <c r="E334">
         <v>3</v>
       </c>
@@ -10112,6 +10511,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D335">
+        <v>1</v>
+      </c>
       <c r="E335">
         <v>3</v>
       </c>
@@ -10141,6 +10543,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D336">
+        <v>4</v>
+      </c>
       <c r="E336">
         <v>3</v>
       </c>
@@ -10170,6 +10575,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D337">
+        <v>4</v>
+      </c>
       <c r="E337">
         <v>3</v>
       </c>
@@ -10199,6 +10607,9 @@
           <t>pH units</t>
         </is>
       </c>
+      <c r="D338">
+        <v>4</v>
+      </c>
       <c r="E338">
         <v>3</v>
       </c>
@@ -10228,6 +10639,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D339">
+        <v>4</v>
+      </c>
       <c r="E339">
         <v>3</v>
       </c>
@@ -10257,6 +10671,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D340">
+        <v>4</v>
+      </c>
       <c r="E340">
         <v>3</v>
       </c>
@@ -10286,6 +10703,9 @@
           <t>metres</t>
         </is>
       </c>
+      <c r="D341">
+        <v>4</v>
+      </c>
       <c r="E341">
         <v>1</v>
       </c>
@@ -10315,6 +10735,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D342">
+        <v>4</v>
+      </c>
       <c r="E342">
         <v>3</v>
       </c>
@@ -10344,6 +10767,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D343">
+        <v>4</v>
+      </c>
       <c r="E343">
         <v>3</v>
       </c>
@@ -10373,6 +10799,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D344">
+        <v>4</v>
+      </c>
       <c r="E344">
         <v>3</v>
       </c>
@@ -10431,6 +10860,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D346">
+        <v>1</v>
+      </c>
       <c r="E346">
         <v>3</v>
       </c>
@@ -10460,6 +10892,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D347">
+        <v>4</v>
+      </c>
       <c r="E347">
         <v>3</v>
       </c>
@@ -10489,6 +10924,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D348">
+        <v>4</v>
+      </c>
       <c r="E348">
         <v>3</v>
       </c>
@@ -10518,6 +10956,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D349">
+        <v>1</v>
+      </c>
       <c r="E349">
         <v>3</v>
       </c>
@@ -10547,6 +10988,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D350">
+        <v>1</v>
+      </c>
       <c r="E350">
         <v>3</v>
       </c>
@@ -10605,6 +11049,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D352">
+        <v>1</v>
+      </c>
       <c r="E352">
         <v>3</v>
       </c>
@@ -10634,6 +11081,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D353">
+        <v>4</v>
+      </c>
       <c r="E353">
         <v>3</v>
       </c>
@@ -10663,6 +11113,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D354">
+        <v>4</v>
+      </c>
       <c r="E354">
         <v>3</v>
       </c>
@@ -10692,6 +11145,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D355">
+        <v>1</v>
+      </c>
       <c r="E355">
         <v>3</v>
       </c>
@@ -10721,6 +11177,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D356">
+        <v>1</v>
+      </c>
       <c r="E356">
         <v>3</v>
       </c>
@@ -10750,6 +11209,9 @@
           <t>microsiemens per centimetre</t>
         </is>
       </c>
+      <c r="D357">
+        <v>4</v>
+      </c>
       <c r="E357">
         <v>3</v>
       </c>
@@ -10779,6 +11241,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D358">
+        <v>1</v>
+      </c>
       <c r="E358">
         <v>3</v>
       </c>
@@ -10808,6 +11273,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D359">
+        <v>4</v>
+      </c>
       <c r="E359">
         <v>3</v>
       </c>
@@ -10837,6 +11305,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D360">
+        <v>1</v>
+      </c>
       <c r="E360">
         <v>3</v>
       </c>
@@ -10866,6 +11337,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D361">
+        <v>4</v>
+      </c>
       <c r="E361">
         <v>3</v>
       </c>
@@ -10895,6 +11369,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D362">
+        <v>1</v>
+      </c>
       <c r="E362">
         <v>3</v>
       </c>
@@ -10924,6 +11401,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D363">
+        <v>1</v>
+      </c>
       <c r="E363">
         <v>3</v>
       </c>
@@ -10953,6 +11433,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D364">
+        <v>1</v>
+      </c>
       <c r="E364">
         <v>3</v>
       </c>
@@ -10982,6 +11465,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D365">
+        <v>4</v>
+      </c>
       <c r="E365">
         <v>3</v>
       </c>
@@ -11011,6 +11497,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D366">
+        <v>4</v>
+      </c>
       <c r="E366">
         <v>3</v>
       </c>
@@ -11040,6 +11529,9 @@
           <t>pH units</t>
         </is>
       </c>
+      <c r="D367">
+        <v>4</v>
+      </c>
       <c r="E367">
         <v>3</v>
       </c>
@@ -11069,6 +11561,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D368">
+        <v>4</v>
+      </c>
       <c r="E368">
         <v>3</v>
       </c>
@@ -11098,6 +11593,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D369">
+        <v>4</v>
+      </c>
       <c r="E369">
         <v>3</v>
       </c>
@@ -11127,6 +11625,9 @@
           <t>metres</t>
         </is>
       </c>
+      <c r="D370">
+        <v>4</v>
+      </c>
       <c r="E370">
         <v>1</v>
       </c>
@@ -11156,6 +11657,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D371">
+        <v>4</v>
+      </c>
       <c r="E371">
         <v>3</v>
       </c>
@@ -11185,6 +11689,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D372">
+        <v>4</v>
+      </c>
       <c r="E372">
         <v>3</v>
       </c>
@@ -11214,6 +11721,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D373">
+        <v>4</v>
+      </c>
       <c r="E373">
         <v>3</v>
       </c>
@@ -11272,6 +11782,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D375">
+        <v>1</v>
+      </c>
       <c r="E375">
         <v>3</v>
       </c>
@@ -11285,17 +11798,889 @@
         <v>0.152</v>
       </c>
     </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>Alkalinity (as calcium carbonate)</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>milligrams per litre</t>
+        </is>
+      </c>
+      <c r="D376">
+        <v>1</v>
+      </c>
+      <c r="E376">
+        <v>3</v>
+      </c>
+      <c r="F376">
+        <v>224</v>
+      </c>
+      <c r="G376">
+        <v>295.333333333333</v>
+      </c>
+      <c r="H376">
+        <v>364</v>
+      </c>
+    </row>
     <row r="377">
-      <c r="A377" s="3" t="inlineStr">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>Ammonia (as N)</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>milligrams per litre</t>
+        </is>
+      </c>
+      <c r="D377">
+        <v>1</v>
+      </c>
+      <c r="E377">
+        <v>3</v>
+      </c>
+      <c r="F377">
+        <v>6.95</v>
+      </c>
+      <c r="G377">
+        <v>12.43</v>
+      </c>
+      <c r="H377">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>Arsenic</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>milligrams per litre</t>
+        </is>
+      </c>
+      <c r="D378">
+        <v>1</v>
+      </c>
+      <c r="E378">
+        <v>3</v>
+      </c>
+      <c r="F378" s="3">
+        <v>0.001</v>
+      </c>
+      <c r="G378" s="3">
+        <v>0.001</v>
+      </c>
+      <c r="H378" s="3">
+        <v>0.001</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>Barium</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>milligrams per litre</t>
+        </is>
+      </c>
+      <c r="D379">
+        <v>1</v>
+      </c>
+      <c r="E379">
+        <v>3</v>
+      </c>
+      <c r="F379">
+        <v>0.467</v>
+      </c>
+      <c r="G379">
+        <v>0.556333333333333</v>
+      </c>
+      <c r="H379">
+        <v>0.69</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>Biochemical oxygen demand</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>milligrams per litre</t>
+        </is>
+      </c>
+      <c r="D380">
+        <v>1</v>
+      </c>
+      <c r="E380">
+        <v>2</v>
+      </c>
+      <c r="F380">
+        <v>2</v>
+      </c>
+      <c r="G380">
+        <v>2</v>
+      </c>
+      <c r="H380">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>Cadmium</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>milligrams per litre</t>
+        </is>
+      </c>
+      <c r="D381">
+        <v>1</v>
+      </c>
+      <c r="E381">
+        <v>3</v>
+      </c>
+      <c r="F381" s="3">
+        <v>0.0001</v>
+      </c>
+      <c r="G381" s="3">
+        <v>0.0001</v>
+      </c>
+      <c r="H381" s="3">
+        <v>0.0001</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>Calcium</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>milligrams per litre</t>
+        </is>
+      </c>
+      <c r="D382">
+        <v>1</v>
+      </c>
+      <c r="E382">
+        <v>3</v>
+      </c>
+      <c r="F382">
+        <v>55</v>
+      </c>
+      <c r="G382">
+        <v>64.3333333333333</v>
+      </c>
+      <c r="H382">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>Chloride</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>milligrams per litre</t>
+        </is>
+      </c>
+      <c r="D383">
+        <v>1</v>
+      </c>
+      <c r="E383">
+        <v>3</v>
+      </c>
+      <c r="F383">
+        <v>22</v>
+      </c>
+      <c r="G383">
+        <v>33</v>
+      </c>
+      <c r="H383">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>Chromium (total)</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>milligrams per litre</t>
+        </is>
+      </c>
+      <c r="D384">
+        <v>1</v>
+      </c>
+      <c r="E384">
+        <v>3</v>
+      </c>
+      <c r="F384" s="3">
+        <v>0.001</v>
+      </c>
+      <c r="G384" s="3">
+        <v>0.001</v>
+      </c>
+      <c r="H384" s="3">
+        <v>0.001</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>Cobalt</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>milligrams per litre</t>
+        </is>
+      </c>
+      <c r="D385">
+        <v>1</v>
+      </c>
+      <c r="E385">
+        <v>3</v>
+      </c>
+      <c r="F385">
+        <v>0.001</v>
+      </c>
+      <c r="G385">
+        <v>0.001</v>
+      </c>
+      <c r="H385">
+        <v>0.001</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>Conductivity</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>microsiemens per centimetre</t>
+        </is>
+      </c>
+      <c r="E386">
+        <v>3</v>
+      </c>
+      <c r="F386">
+        <v>526</v>
+      </c>
+      <c r="G386">
+        <v>637.666666666667</v>
+      </c>
+      <c r="H386">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>milligrams per litre</t>
+        </is>
+      </c>
+      <c r="D387">
+        <v>1</v>
+      </c>
+      <c r="E387">
+        <v>3</v>
+      </c>
+      <c r="F387" s="3">
+        <v>0.001</v>
+      </c>
+      <c r="G387" s="3">
+        <v>0.001</v>
+      </c>
+      <c r="H387" s="3">
+        <v>0.001</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>Fluoride</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>milligrams per litre</t>
+        </is>
+      </c>
+      <c r="D388">
+        <v>1</v>
+      </c>
+      <c r="E388">
+        <v>3</v>
+      </c>
+      <c r="F388" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="G388" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="H388" s="3">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>milligrams per litre</t>
+        </is>
+      </c>
+      <c r="D389">
+        <v>1</v>
+      </c>
+      <c r="E389">
+        <v>3</v>
+      </c>
+      <c r="F389" s="3">
+        <v>0.001</v>
+      </c>
+      <c r="G389" s="3">
+        <v>0.001</v>
+      </c>
+      <c r="H389" s="3">
+        <v>0.001</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>Magnesium</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>milligrams per litre</t>
+        </is>
+      </c>
+      <c r="D390">
+        <v>1</v>
+      </c>
+      <c r="E390">
+        <v>3</v>
+      </c>
+      <c r="F390">
+        <v>7</v>
+      </c>
+      <c r="G390">
+        <v>7.66666666666667</v>
+      </c>
+      <c r="H390">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>Manganese</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>milligrams per litre</t>
+        </is>
+      </c>
+      <c r="D391">
+        <v>1</v>
+      </c>
+      <c r="E391">
+        <v>3</v>
+      </c>
+      <c r="F391">
+        <v>0.497</v>
+      </c>
+      <c r="G391">
+        <v>0.996333333333333</v>
+      </c>
+      <c r="H391">
+        <v>1.85</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>Mercury</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>milligrams per litre</t>
+        </is>
+      </c>
+      <c r="D392">
+        <v>1</v>
+      </c>
+      <c r="E392">
+        <v>3</v>
+      </c>
+      <c r="F392" s="3">
+        <v>0.0001</v>
+      </c>
+      <c r="G392" s="3">
+        <v>0.0001</v>
+      </c>
+      <c r="H392" s="3">
+        <v>0.0001</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>Nickel</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>milligrams per litre</t>
+        </is>
+      </c>
+      <c r="D393">
+        <v>1</v>
+      </c>
+      <c r="E393">
+        <v>3</v>
+      </c>
+      <c r="F393">
+        <v>0.001</v>
+      </c>
+      <c r="G393">
+        <v>0.002</v>
+      </c>
+      <c r="H393">
+        <v>0.003</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>Nitrate (as N)</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>milligrams per litre</t>
+        </is>
+      </c>
+      <c r="D394">
+        <v>1</v>
+      </c>
+      <c r="E394">
+        <v>3</v>
+      </c>
+      <c r="F394" s="3">
+        <v>0.01</v>
+      </c>
+      <c r="G394">
+        <v>0.0666666666666667</v>
+      </c>
+      <c r="H394">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>Nitrite (as N)</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>milligrams per litre</t>
+        </is>
+      </c>
+      <c r="D395">
+        <v>1</v>
+      </c>
+      <c r="E395">
+        <v>3</v>
+      </c>
+      <c r="F395" s="3">
+        <v>0.01</v>
+      </c>
+      <c r="G395" s="3">
+        <v>0.01</v>
+      </c>
+      <c r="H395" s="3">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>pH</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>pH units</t>
+        </is>
+      </c>
+      <c r="E396">
+        <v>3</v>
+      </c>
+      <c r="F396">
+        <v>6.6</v>
+      </c>
+      <c r="G396">
+        <v>7.06</v>
+      </c>
+      <c r="H396">
+        <v>7.46</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>Potassium</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>milligrams per litre</t>
+        </is>
+      </c>
+      <c r="D397">
+        <v>1</v>
+      </c>
+      <c r="E397">
+        <v>3</v>
+      </c>
+      <c r="F397">
+        <v>21</v>
+      </c>
+      <c r="G397">
+        <v>25.3333333333333</v>
+      </c>
+      <c r="H397">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>Sodium</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>milligrams per litre</t>
+        </is>
+      </c>
+      <c r="D398">
+        <v>1</v>
+      </c>
+      <c r="E398">
+        <v>3</v>
+      </c>
+      <c r="F398">
+        <v>20</v>
+      </c>
+      <c r="G398">
+        <v>27.6666666666667</v>
+      </c>
+      <c r="H398">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>Sulfate</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>milligrams per litre</t>
+        </is>
+      </c>
+      <c r="D399">
+        <v>1</v>
+      </c>
+      <c r="E399">
+        <v>3</v>
+      </c>
+      <c r="F399">
+        <v>1</v>
+      </c>
+      <c r="G399">
+        <v>1</v>
+      </c>
+      <c r="H399">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>Total Dissolved Solids</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>milligrams per litre</t>
+        </is>
+      </c>
+      <c r="D400">
+        <v>1</v>
+      </c>
+      <c r="E400">
+        <v>3</v>
+      </c>
+      <c r="F400">
+        <v>342</v>
+      </c>
+      <c r="G400">
+        <v>414.666666666667</v>
+      </c>
+      <c r="H400">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>Total Organic Carbon</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>milligrams per litre</t>
+        </is>
+      </c>
+      <c r="D401">
+        <v>1</v>
+      </c>
+      <c r="E401">
+        <v>3</v>
+      </c>
+      <c r="F401">
+        <v>5</v>
+      </c>
+      <c r="G401">
+        <v>7.66666666666667</v>
+      </c>
+      <c r="H401">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>Zinc</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>milligrams per litre</t>
+        </is>
+      </c>
+      <c r="D402">
+        <v>1</v>
+      </c>
+      <c r="E402">
+        <v>3</v>
+      </c>
+      <c r="F402" s="3">
+        <v>0.005</v>
+      </c>
+      <c r="G402">
+        <v>0.0153333333333333</v>
+      </c>
+      <c r="H402">
+        <v>0.035</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" s="3" t="inlineStr">
         <is>
           <t>Note on values below the analytical detection limit. Where a result was below the detection limit for the analysis, the figure shown is that detection limit rather than a measured concentration, in accordance with the convention stated in the licence Dictionary. The exception is Methane, which the field instrument records as zero when none is detected. Such figures are shown in grey italics.</t>
         </is>
       </c>
     </row>
-    <row r="378">
-      <c r="A378" s="3" t="inlineStr">
+    <row r="405">
+      <c r="A405" s="3" t="inlineStr">
         <is>
           <t>A Lowest or Highest value in grey italics was attained only by below-detection results. A Mean in grey italics indicates that every result for that monitoring point and pollutant was below detection. Figures in normal type are measured values.</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" s="3" t="inlineStr">
+        <is>
+          <t>No. of samples required is taken from licence conditions M2.2 and M2.3 (Quarterly = 4, Yearly = 1). It is left blank where the licence sets no requirement for that pollutant at that point, and for points 2 and 3, where condition M2.4(a) Special Frequency 1 requires sampling within the first 24 hours of each discharge rather than a fixed number of samples.</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" s="3" t="inlineStr">
+        <is>
+          <t>At point 1 the number of samples collected counts individual grid locations. The quarterly requirement refers to monitoring events.</t>
         </is>
       </c>
     </row>
